--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
@@ -427,7 +427,11 @@
           <t>Module</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -435,7 +439,11 @@
           <t>Professor</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DING</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -443,7 +451,11 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -451,7 +463,11 @@
           <t>Code</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -500,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>661</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -518,9 +534,6 @@
         <is>
           <t>Note pour valider</t>
         </is>
-      </c>
-      <c r="B11" t="n">
-        <v>111</v>
       </c>
     </row>
     <row r="12"/>
@@ -532,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>Ydszi</t>
         </is>
       </c>
     </row>
@@ -544,7 +557,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>QDEDAIALLY</t>
         </is>
       </c>
     </row>
@@ -555,7 +568,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -566,7 +579,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G78A</t>
+          <t>G78G</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G78G</t>
+          <t>G78H</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ydszi</t>
+          <t>Yasil</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QDEDAIALLY</t>
+          <t>RHEAATALLY</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>1111</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="5">
@@ -730,7 +730,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Yasil</t>
+          <t>YASIL</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63807.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -703,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>1131</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
